--- a/stories/arbres/TREE-DIF-014.xlsx
+++ b/stories/arbres/TREE-DIF-014.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Lila est avec maman, sous le pommier. Lila a envie de jouer. maman est là, tout près. On va apprendre : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila écoute maman. Lila entend les mots : tailles différentes, jouer ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lila se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On range un objet. maman dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lila se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers le bac à sable. Un chat miaule une fois. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lila se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On range un objet.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Plus petit ou plus grand.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : inviter ; jouer. Lila respire. Lila retient : tailles différentes, jouer ensemble. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2582,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2751,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3853,6 +3946,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4017,6 +4115,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4282,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4449,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4616,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4783,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4950,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5117,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5310,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5479,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5646,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5813,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5980,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6147,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6314,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6343,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lila se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On dit merci. maman dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lila se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6481,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers le toboggan. Les chaussures font toc toc. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lila se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On dit merci.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6663,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Plus petit ou plus grand.</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6836,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : inviter ; jouer. Lila respire. Lila retient : tailles différentes, jouer ensemble. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7027,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7194,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7193,6 +7387,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7357,6 +7556,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7723,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7890,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8057,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8224,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8391,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8558,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8517,6 +8751,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8681,6 +8920,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9087,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9254,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9421,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9588,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9755,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9922,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9841,6 +10115,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10005,6 +10284,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10451,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10618,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10785,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10653,6 +10952,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11119,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10839,7 +11148,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Lila va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lila se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Lila va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lila se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10977,6 +11286,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Lila va vers les balançoires. La couverture est douce. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lila se souvient : tailles différentes, jouer ensemble. Voici le geste : inviter ; jouer. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11468,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Plus petit ou plus grand.</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11641,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : inviter ; jouer. Lila respire. Lila retient : tailles différentes, jouer ensemble. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11832,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +11999,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11857,6 +12192,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12021,6 +12361,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12528,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12695,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12862,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13029,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13196,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13363,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13181,6 +13556,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13345,6 +13725,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13892,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14059,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14226,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14393,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14560,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14727,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14505,6 +14920,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14669,6 +15089,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15256,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15423,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15590,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15317,6 +15757,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15924,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16020,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-014.xlsx
+++ b/stories/arbres/TREE-DIF-014.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Lila est avec maman, sous le pommier. Lila a envie de jouer. maman est là, tout près. On va apprendre : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila écoute maman. Lila entend les mots : tailles différentes, jouer ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? Plus petit ou plus grand.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : inviter ; jouer. Lila respire. Lila retient : tailles différentes, jouer ensemble. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Lila a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Lila rejoint Tom. Le vent est doux. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Lila rejoint Léa. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Lila rejoint Sami. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Lila a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3953,6 +3973,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4120,6 +4141,7 @@
           <t>narrateur|Lila rejoint Tom. Le sol est un peu froid. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4287,6 +4309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4454,6 +4477,7 @@
           <t>narrateur|Lila rejoint Léa. Une feuille tombe. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4621,6 +4645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4788,6 +4813,7 @@
           <t>narrateur|Lila rejoint Sami. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4955,6 +4981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5122,6 +5149,7 @@
           <t>narrateur|Lila a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5317,6 +5345,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5484,6 +5513,7 @@
           <t>narrateur|Lila rejoint Tom. Une feuille tombe. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5651,6 +5681,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5818,6 +5849,7 @@
           <t>narrateur|Lila rejoint Léa. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5985,6 +6017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6152,6 +6185,7 @@
           <t>narrateur|Lila rejoint Sami. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6319,6 +6353,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6487,6 +6522,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6670,6 +6706,7 @@
           <t>narrateur|Que fait-on ? Plus petit ou plus grand.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6841,6 +6878,7 @@
           <t>narrateur|Oui. Voici le geste : inviter ; jouer. Lila respire. Lila retient : tailles différentes, jouer ensemble. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7032,6 +7070,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7199,6 +7238,7 @@
           <t>narrateur|Lila a choisi le ballon. Le vent est doux. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7394,6 +7434,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7561,6 +7602,7 @@
           <t>narrateur|Lila rejoint Tom. Le sol est un peu froid. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7728,6 +7770,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7895,6 +7938,7 @@
           <t>narrateur|Lila rejoint Léa. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8062,6 +8106,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8229,6 +8274,7 @@
           <t>narrateur|Lila rejoint Sami. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8396,6 +8442,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8563,6 +8610,7 @@
           <t>narrateur|Lila a choisi le seau. Le sol est un peu froid. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8758,6 +8806,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8925,6 +8974,7 @@
           <t>narrateur|Lila rejoint Tom. Une feuille tombe. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9092,6 +9142,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9259,6 +9310,7 @@
           <t>narrateur|Lila rejoint Léa. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9426,6 +9478,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9593,6 +9646,7 @@
           <t>narrateur|Lila rejoint Sami. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9760,6 +9814,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9927,6 +9982,7 @@
           <t>narrateur|Lila a choisi le doudou. Une feuille tombe. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10122,6 +10178,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10289,6 +10346,7 @@
           <t>narrateur|Lila rejoint Tom. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10456,6 +10514,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10623,6 +10682,7 @@
           <t>narrateur|Lila rejoint Léa. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10790,6 +10850,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10957,6 +11018,7 @@
           <t>narrateur|Lila rejoint Sami. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11124,6 +11186,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11292,6 +11355,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11475,6 +11539,7 @@
           <t>narrateur|Que fait-on ? Plus petit ou plus grand.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11646,6 +11711,7 @@
           <t>narrateur|Oui. Voici le geste : inviter ; jouer. Lila respire. Lila retient : tailles différentes, jouer ensemble. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11837,6 +11903,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12004,6 +12071,7 @@
           <t>narrateur|Lila a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12199,6 +12267,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12366,6 +12435,7 @@
           <t>narrateur|Lila rejoint Tom. Une feuille tombe. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12533,6 +12603,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12700,6 +12771,7 @@
           <t>narrateur|Lila rejoint Léa. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12867,6 +12939,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13034,6 +13107,7 @@
           <t>narrateur|Lila rejoint Sami. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13201,6 +13275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13368,6 +13443,7 @@
           <t>narrateur|Lila a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13563,6 +13639,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13730,6 +13807,7 @@
           <t>narrateur|Lila rejoint Tom. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13897,6 +13975,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14064,6 +14143,7 @@
           <t>narrateur|Lila rejoint Léa. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14231,6 +14311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14398,6 +14479,7 @@
           <t>narrateur|Lila rejoint Sami. La lumière est claire. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14565,6 +14647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14732,6 +14815,7 @@
           <t>narrateur|Lila a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : inviter ; jouer. Lila répète tout bas : tailles différentes, jouer ensemble. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14927,6 +15011,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15094,6 +15179,7 @@
           <t>narrateur|Lila rejoint Tom. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15261,6 +15347,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15428,6 +15515,7 @@
           <t>narrateur|Lila rejoint Léa. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15595,6 +15683,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15762,6 +15851,7 @@
           <t>narrateur|Lila rejoint Sami. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Lila a appris : Plus petit ou plus grand. Voici le geste : inviter ; jouer. Lila a entendu : tailles différentes, jouer ensemble. Lila dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15929,6 +16019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15947,7 +16038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16027,6 +16118,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16041,7 +16146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16228,6 +16333,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-014.xlsx
+++ b/stories/arbres/TREE-DIF-014.xlsx
@@ -3116,17 +3116,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! Le panier attend en bas, plein d'ombre. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le grain de sève, sur le tronc. Elle est à toi, un moment. Vous l'avez fait glisser, à deux hauteurs. Le grain de sève luit, à la hauteur de Nino.</t>
+          <t>Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! Le panier attend en bas, plein d'ombre. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le grain de sève, sur le tronc. Elle est à toi, un moment. La branche et les mains ont fait le travail. Le grain de sève luit, à la hauteur de Nino.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! Le panier attend en bas, plein d'ombre. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Elle est à toi, un moment. Vous l'avez fait glisser, à deux hauteurs. Le grain de sève luit, à la hauteur de Nino.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! Le panier attend en bas, plein d'ombre. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Elle est à toi, un moment. La branche et les mains ont fait le travail. Le grain de sève luit, à la hauteur de Nino.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! Le panier attend en bas, plein d'ombre. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Elle est à toi, un moment. Vous l'avez fait glisser, à deux hauteurs. Le grain de sève luit, à la hauteur de Nino. [pause]</t>
+          <t>Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! Le panier attend en bas, plein d'ombre. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Elle est à toi, un moment. La branche et les mains ont fait le travail. Le grain de sève luit, à la hauteur de Nino. [pause]</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -3270,7 +3270,7 @@
 narrateur|Mila observe l'objet, écoute la branche.
 narrateur|Elle retrouve le grain de sève, sur le tronc.
 enfant-f|Elle est à toi, un moment.
-maman|Vous l'avez fait glisser, à deux hauteurs.
+maman|La branche et les mains ont fait le travail.
 narrateur|Le grain de sève luit, à la hauteur de Nino.</t>
         </is>
       </c>
@@ -5010,17 +5010,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. Le panier devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le grain de sève, sur le tronc. Vous y arrivez, à deux hauteurs. Un brin reste collé au grain de sève.</t>
+          <t>Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. Le panier devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le grain de sève, sur le tronc. Le nid dans l'herbe a tenu le fruit. Un brin reste collé au grain de sève.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. Le panier devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Vous y arrivez, à deux hauteurs. Un brin reste collé au grain de sève.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. Le panier devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Le nid dans l'herbe a tenu le fruit. Un brin reste collé au grain de sève.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. Le panier devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Vous y arrivez, à deux hauteurs. Un brin reste collé au grain de sève. [pause]</t>
+          <t>Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. Le panier devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Le nid dans l'herbe a tenu le fruit. Un brin reste collé au grain de sève. [pause]</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -5164,7 +5164,7 @@
 narrateur|Deux paires de mains tiennent le fruit.
 narrateur|Mila observe l'objet, écoute l'herbe.
 narrateur|Elle retrouve le grain de sève, sur le tronc.
-maman|Vous y arrivez, à deux hauteurs.
+maman|Le nid dans l'herbe a tenu le fruit.
 narrateur|Un brin reste collé au grain de sève.</t>
         </is>
       </c>
@@ -6152,17 +6152,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Reste en bas, Nino. Je tends, d'ici. Nino tend le panier, bras tout courts. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le grain de sève, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Vos bras n'avaient pas la même longueur. Le grain de sève reste collé, comme un stop.</t>
+          <t>Reste en bas, Nino. Je tends, d'ici. Nino tend le panier, bras tout courts. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le grain de sève, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Tes mains d'en bas ont reçu le fruit. Le grain de sève reste collé, comme un stop.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Reste en bas, Nino. Je tends, d'ici. Nino tend le panier, bras tout courts. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Vos bras n'avaient pas la même longueur. Le grain de sève reste collé, comme un stop.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Reste en bas, Nino. Je tends, d'ici. Nino tend le panier, bras tout courts. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Tes mains d'en bas ont reçu le fruit. Le grain de sève reste collé, comme un stop.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Reste en bas, Nino. Je tends, d'ici. Nino tend le panier, bras tout courts. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Vos bras n'avaient pas la même longueur. Le grain de sève reste collé, comme un stop. [pause]</t>
+          <t>Reste en bas, Nino. Je tends, d'ici. Nino tend le panier, bras tout courts. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Tes mains d'en bas ont reçu le fruit. Le grain de sève reste collé, comme un stop. [pause]</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -6306,7 +6306,7 @@
 narrateur|Elle retrouve le grain de sève, à la hauteur de Nino.
 papa|Chacun a fait sa part.
 enfant-f|Elle sent le soleil.
-maman|Vos bras n'avaient pas la même longueur.
+maman|Tes mains d'en bas ont reçu le fruit.
 narrateur|Le grain de sève reste collé, comme un stop.</t>
         </is>
       </c>
@@ -6528,17 +6528,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>On monte à deux ? Oui, tout léger. Papa pose le panier sur le banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le grain de sève, sur le tronc. Vous avez tiré, chacun à sa hauteur. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres.</t>
+          <t>On monte à deux ? Oui, tout léger. Papa pose le panier sur le banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le grain de sève, sur le tronc. Chacun a tiré, sans se presser. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On monte à deux ? Oui, tout léger. Papa pose le panier sur le banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Vous avez tiré, chacun à sa hauteur. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On monte à deux ? Oui, tout léger. Papa pose le panier sur le banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Chacun a tiré, sans se presser. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>On monte à deux ? Oui, tout léger. Papa pose le panier sur le banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Vous avez tiré, chacun à sa hauteur. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres. [pause]</t>
+          <t>On monte à deux ? Oui, tout léger. Papa pose le panier sur le banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Chacun a tiré, sans se presser. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres. [pause]</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -6681,7 +6681,7 @@
 enfant-m|Je la sens.
 narrateur|Mila observe l'objet, écoute le banc.
 narrateur|Elle retrouve le grain de sève, sur le tronc.
-maman|Vous avez tiré, chacun à sa hauteur.
+maman|Chacun a tiré, sans se presser.
 papa|Le banc est resté à sa place.
 narrateur|Le grain de sève luit entre leurs deux ombres.</t>
         </is>
@@ -8430,17 +8430,17 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! La nappe attend en bas, un peu verte. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le grain de sève, sur le tronc. Elle est à toi, un moment. Vous l'avez fait glisser, à deux hauteurs. Le grain de sève luit, à la hauteur de Nino.</t>
+          <t>Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! La nappe attend en bas, un peu verte. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le grain de sève, sur le tronc. Elle est à toi, un moment. La branche et les mains ont fait le travail. Le grain de sève luit, à la hauteur de Nino.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! La nappe attend en bas, un peu verte. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Elle est à toi, un moment. Vous l'avez fait glisser, à deux hauteurs. Le grain de sève luit, à la hauteur de Nino.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! La nappe attend en bas, un peu verte. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Elle est à toi, un moment. La branche et les mains ont fait le travail. Le grain de sève luit, à la hauteur de Nino.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! La nappe attend en bas, un peu verte. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Elle est à toi, un moment. Vous l'avez fait glisser, à deux hauteurs. Le grain de sève luit, à la hauteur de Nino. [pause]</t>
+          <t>Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! La nappe attend en bas, un peu verte. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Elle est à toi, un moment. La branche et les mains ont fait le travail. Le grain de sève luit, à la hauteur de Nino. [pause]</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -8584,7 +8584,7 @@
 narrateur|Mila observe l'objet, écoute la branche.
 narrateur|Elle retrouve le grain de sève, sur le tronc.
 enfant-f|Elle est à toi, un moment.
-maman|Vous l'avez fait glisser, à deux hauteurs.
+maman|La branche et les mains ont fait le travail.
 narrateur|Le grain de sève luit, à la hauteur de Nino.</t>
         </is>
       </c>
@@ -10324,17 +10324,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. La nappe devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le grain de sève, sur le tronc. Vous y arrivez, à deux hauteurs. Un brin reste collé au grain de sève.</t>
+          <t>Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. La nappe devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le grain de sève, sur le tronc. Le nid dans l'herbe a tenu le fruit. Un brin reste collé au grain de sève.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. La nappe devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Vous y arrivez, à deux hauteurs. Un brin reste collé au grain de sève.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. La nappe devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Le nid dans l'herbe a tenu le fruit. Un brin reste collé au grain de sève.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. La nappe devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Vous y arrivez, à deux hauteurs. Un brin reste collé au grain de sève. [pause]</t>
+          <t>Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. La nappe devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Le nid dans l'herbe a tenu le fruit. Un brin reste collé au grain de sève. [pause]</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -10478,7 +10478,7 @@
 narrateur|Deux paires de mains tiennent le fruit.
 narrateur|Mila observe l'objet, écoute l'herbe.
 narrateur|Elle retrouve le grain de sève, sur le tronc.
-maman|Vous y arrivez, à deux hauteurs.
+maman|Le nid dans l'herbe a tenu le fruit.
 narrateur|Un brin reste collé au grain de sève.</t>
         </is>
       </c>
@@ -10511,17 +10511,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Leurs chaussettes portent de l'herbe. Papa a ouvert un chemin. On l'a prise. L'herbe vous a laissé la place. Changez le linge des pieds, d'abord. La nappe garde un brin, dans un carreau. Nino aligne la pomme sous le grain de sève. Tu gardes quoi, de l'herbe ? Surtout l'herbe haute. L'herbe a laissé une virgule verte.</t>
+          <t>Leurs chaussettes portent de l'herbe. Papa a ouvert un chemin. On l'a prise. L'herbe vous a laissé la place. Changez le linge des pieds, d'abord. La nappe garde un brin, dans un carreau. Nino aligne la pomme sous le grain de sève. Tu gardes quoi, de l'herbe ? Surtout l'herbe haute. Un brin vert dort sous la nappe.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Leurs chaussettes portent de l'herbe. Papa a ouvert un chemin. On l'a prise. L'herbe vous a laissé la place. Changez le linge des pieds, d'abord. La nappe garde un brin, dans un carreau. Nino aligne la pomme sous le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;. Tu gardes quoi, de l'herbe ? Surtout l'herbe haute. L'herbe a laissé une virgule verte.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Leurs chaussettes portent de l'herbe. Papa a ouvert un chemin. On l'a prise. L'herbe vous a laissé la place. Changez le linge des pieds, d'abord. La nappe garde un brin, dans un carreau. Nino aligne la pomme sous le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;. Tu gardes quoi, de l'herbe ? Surtout l'herbe haute. Un brin vert dort sous la nappe.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Leurs chaussettes portent de l'herbe. Papa a ouvert un chemin. On l'a prise. L'herbe vous a laissé la place. Changez le linge des pieds, d'abord. La nappe garde un brin, dans un carreau. Nino aligne la pomme sous le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;. Tu gardes quoi, de l'herbe ? Surtout l'herbe haute. L'herbe a laissé une virgule verte.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Leurs chaussettes portent de l'herbe. Papa a ouvert un chemin. On l'a prise. L'herbe vous a laissé la place. Changez le linge des pieds, d'abord. La nappe garde un brin, dans un carreau. Nino aligne la pomme sous le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;. Tu gardes quoi, de l'herbe ? Surtout l'herbe haute. Un brin vert dort sous la nappe.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -10668,7 +10668,7 @@
 narrateur|Nino aligne la pomme sous le grain de sève.
 maman|Tu gardes quoi, de l'herbe ?
 enfant-f|Surtout l'herbe haute.
-narrateur|L'herbe a laissé une virgule verte.</t>
+narrateur|Un brin vert dort sous la nappe.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
@@ -11466,17 +11466,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Reste en bas, Nino. Je tends, d'ici. Nino tend la nappe, bras tout courts. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le grain de sève, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Vos bras n'avaient pas la même longueur. Le grain de sève reste collé, comme un stop.</t>
+          <t>Reste en bas, Nino. Je tends, d'ici. Nino tend la nappe, bras tout courts. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le grain de sève, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Tes mains d'en bas ont reçu le fruit. Le grain de sève reste collé, comme un stop.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Reste en bas, Nino. Je tends, d'ici. Nino tend la nappe, bras tout courts. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Vos bras n'avaient pas la même longueur. Le grain de sève reste collé, comme un stop.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Reste en bas, Nino. Je tends, d'ici. Nino tend la nappe, bras tout courts. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Tes mains d'en bas ont reçu le fruit. Le grain de sève reste collé, comme un stop.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Reste en bas, Nino. Je tends, d'ici. Nino tend la nappe, bras tout courts. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Vos bras n'avaient pas la même longueur. Le grain de sève reste collé, comme un stop. [pause]</t>
+          <t>Reste en bas, Nino. Je tends, d'ici. Nino tend la nappe, bras tout courts. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Tes mains d'en bas ont reçu le fruit. Le grain de sève reste collé, comme un stop. [pause]</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -11620,7 +11620,7 @@
 narrateur|Elle retrouve le grain de sève, à la hauteur de Nino.
 papa|Chacun a fait sa part.
 enfant-f|Elle sent le soleil.
-maman|Vos bras n'avaient pas la même longueur.
+maman|Tes mains d'en bas ont reçu le fruit.
 narrateur|Le grain de sève reste collé, comme un stop.</t>
         </is>
       </c>
@@ -11842,17 +11842,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>On monte à deux ? Oui, tout léger. Papa pose la nappe sur le banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le grain de sève, sur le tronc. Vous avez tiré, chacun à sa hauteur. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres.</t>
+          <t>On monte à deux ? Oui, tout léger. Papa pose la nappe sur le banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le grain de sève, sur le tronc. Chacun a tiré, sans se presser. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On monte à deux ? Oui, tout léger. Papa pose la nappe sur le banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Vous avez tiré, chacun à sa hauteur. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On monte à deux ? Oui, tout léger. Papa pose la nappe sur le banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Chacun a tiré, sans se presser. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>On monte à deux ? Oui, tout léger. Papa pose la nappe sur le banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Vous avez tiré, chacun à sa hauteur. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres. [pause]</t>
+          <t>On monte à deux ? Oui, tout léger. Papa pose la nappe sur le banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Chacun a tiré, sans se presser. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres. [pause]</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -11995,7 +11995,7 @@
 enfant-m|Je la sens.
 narrateur|Mila observe l'objet, écoute le banc.
 narrateur|Elle retrouve le grain de sève, sur le tronc.
-maman|Vous avez tiré, chacun à sa hauteur.
+maman|Chacun a tiré, sans se presser.
 papa|Le banc est resté à sa place.
 narrateur|Le grain de sève luit entre leurs deux ombres.</t>
         </is>
@@ -13744,17 +13744,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! Le tabouret attend en bas, un peu humide. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le grain de sève, sur le tronc. Elle est à toi, un moment. Vous l'avez fait glisser, à deux hauteurs. Le grain de sève luit, à la hauteur de Nino.</t>
+          <t>Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! Le tabouret attend en bas, un peu humide. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le grain de sève, sur le tronc. Elle est à toi, un moment. La branche et les mains ont fait le travail. Le grain de sève luit, à la hauteur de Nino.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! Le tabouret attend en bas, un peu humide. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Elle est à toi, un moment. Vous l'avez fait glisser, à deux hauteurs. Le grain de sève luit, à la hauteur de Nino.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! Le tabouret attend en bas, un peu humide. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Elle est à toi, un moment. La branche et les mains ont fait le travail. Le grain de sève luit, à la hauteur de Nino.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! Le tabouret attend en bas, un peu humide. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Elle est à toi, un moment. Vous l'avez fait glisser, à deux hauteurs. Le grain de sève luit, à la hauteur de Nino. [pause]</t>
+          <t>Je soulève la branche. Je te tiens, Mila. Mila lève le bois, plus haute que Nino. Je vois la pomme ! Le tabouret attend en bas, un peu humide. Nino tend les deux mains, sans se presser. La pomme glisse vers lui, hors du vert. Mila observe l'objet, écoute la branche. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Elle est à toi, un moment. La branche et les mains ont fait le travail. Le grain de sève luit, à la hauteur de Nino. [pause]</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -13898,7 +13898,7 @@
 narrateur|Mila observe l'objet, écoute la branche.
 narrateur|Elle retrouve le grain de sève, sur le tronc.
 enfant-f|Elle est à toi, un moment.
-maman|Vous l'avez fait glisser, à deux hauteurs.
+maman|La branche et les mains ont fait le travail.
 narrateur|Le grain de sève luit, à la hauteur de Nino.</t>
         </is>
       </c>
@@ -15638,17 +15638,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. Le tabouret devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le grain de sève, sur le tronc. Vous y arrivez, à deux hauteurs. Un brin reste collé au grain de sève.</t>
+          <t>Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. Le tabouret devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le grain de sève, sur le tronc. Le nid dans l'herbe a tenu le fruit. Un brin reste collé au grain de sève.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. Le tabouret devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Vous y arrivez, à deux hauteurs. Un brin reste collé au grain de sève.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. Le tabouret devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Le nid dans l'herbe a tenu le fruit. Un brin reste collé au grain de sève.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. Le tabouret devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Vous y arrivez, à deux hauteurs. Un brin reste collé au grain de sève. [pause]</t>
+          <t>Papa, écarte un peu ? Je fais un chemin, tout étroit. L'herbe s'ouvre, comme une porte. La pomme rouge apparaît, collée. Le tabouret devient un nid, dans l'herbe. On la prend. Oui. Deux paires de mains tiennent le fruit. Mila observe l'objet, écoute l'herbe. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Le nid dans l'herbe a tenu le fruit. Un brin reste collé au grain de sève. [pause]</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -15792,7 +15792,7 @@
 narrateur|Deux paires de mains tiennent le fruit.
 narrateur|Mila observe l'objet, écoute l'herbe.
 narrateur|Elle retrouve le grain de sève, sur le tronc.
-maman|Vous y arrivez, à deux hauteurs.
+maman|Le nid dans l'herbe a tenu le fruit.
 narrateur|Un brin reste collé au grain de sève.</t>
         </is>
       </c>
@@ -16780,17 +16780,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Reste en bas, Nino. Je tends, d'ici. Nino pousse le tabouret, tout près. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le grain de sève, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Vos bras n'avaient pas la même longueur. Le grain de sève reste collé, comme un stop.</t>
+          <t>Reste en bas, Nino. Je tends, d'ici. Nino pousse le tabouret, tout près. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le grain de sève, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Tes mains d'en bas ont reçu le fruit. Le grain de sève reste collé, comme un stop.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Reste en bas, Nino. Je tends, d'ici. Nino pousse le tabouret, tout près. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Vos bras n'avaient pas la même longueur. Le grain de sève reste collé, comme un stop.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Reste en bas, Nino. Je tends, d'ici. Nino pousse le tabouret, tout près. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Tes mains d'en bas ont reçu le fruit. Le grain de sève reste collé, comme un stop.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Reste en bas, Nino. Je tends, d'ici. Nino pousse le tabouret, tout près. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Vos bras n'avaient pas la même longueur. Le grain de sève reste collé, comme un stop. [pause]</t>
+          <t>Reste en bas, Nino. Je tends, d'ici. Nino pousse le tabouret, tout près. Mila fait basculer la pomme, tout léger. Le fruit tombe dans les mains d'en bas. Je la tiens ! Mila observe l'objet, écoute les mains. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, à la hauteur de Nino. Chacun a fait sa part. Elle sent le soleil. Tes mains d'en bas ont reçu le fruit. Le grain de sève reste collé, comme un stop. [pause]</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -16934,7 +16934,7 @@
 narrateur|Elle retrouve le grain de sève, à la hauteur de Nino.
 papa|Chacun a fait sa part.
 enfant-f|Elle sent le soleil.
-maman|Vos bras n'avaient pas la même longueur.
+maman|Tes mains d'en bas ont reçu le fruit.
 narrateur|Le grain de sève reste collé, comme un stop.</t>
         </is>
       </c>
@@ -17156,17 +17156,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>On monte à deux ? Oui, tout léger. Papa pose le tabouret près du banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le grain de sève, sur le tronc. Vous avez tiré, chacun à sa hauteur. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres.</t>
+          <t>On monte à deux ? Oui, tout léger. Papa pose le tabouret près du banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le grain de sève, sur le tronc. Chacun a tiré, sans se presser. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On monte à deux ? Oui, tout léger. Papa pose le tabouret près du banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Vous avez tiré, chacun à sa hauteur. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On monte à deux ? Oui, tout léger. Papa pose le tabouret près du banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le &lt;emphasis level="moderate"&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Chacun a tiré, sans se presser. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>On monte à deux ? Oui, tout léger. Papa pose le tabouret près du banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Vous avez tiré, chacun à sa hauteur. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres. [pause]</t>
+          <t>On monte à deux ? Oui, tout léger. Papa pose le tabouret près du banc, entre eux. Papa tient le bois, tout ferme. Mila et Nino tendent, sans se presser. Elle vient ! Je la sens. Mila observe l'objet, écoute le banc. Elle retrouve le &lt;emphasis&gt;grain de sève&lt;/emphasis&gt;, sur le tronc. Chacun a tiré, sans se presser. Le banc est resté à sa place. Le grain de sève luit entre leurs deux ombres. [pause]</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -17309,7 +17309,7 @@
 enfant-m|Je la sens.
 narrateur|Mila observe l'objet, écoute le banc.
 narrateur|Elle retrouve le grain de sève, sur le tronc.
-maman|Vous avez tiré, chacun à sa hauteur.
+maman|Chacun a tiré, sans se presser.
 papa|Le banc est resté à sa place.
 narrateur|Le grain de sève luit entre leurs deux ombres.</t>
         </is>
@@ -17526,7 +17526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17632,6 +17632,13 @@
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
